--- a/inventories/optimized/lci-Salar-de-Pastos-Grandes.xlsx
+++ b/inventories/optimized/lci-Salar-de-Pastos-Grandes.xlsx
@@ -813,7 +813,7 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>-0.008217138949518449</v>
+        <v>-0.008217138949518451</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -898,7 +898,7 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>0.02474001677726591</v>
+        <v>0.02474001677726592</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -1213,7 +1213,7 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.3771335979239749</v>
+        <v>0.3350169153839317</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1230,7 +1230,7 @@
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.5285830025950314</v>
+        <v>0.5812288557700854</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         <v>39</v>
       </c>
       <c r="B62">
-        <v>0.13533213428111</v>
+        <v>0.148810955272803</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1264,7 +1264,7 @@
         <v>42</v>
       </c>
       <c r="B63">
-        <v>0.09428339948099373</v>
+        <v>0.08375422884598292</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1379,7 +1379,7 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>0.0004885719404391602</v>
+        <v>0.0004885719404391603</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1843,7 +1843,7 @@
         <v>40</v>
       </c>
       <c r="B118">
-        <v>10.14276337427729</v>
+        <v>11.41786181109403</v>
       </c>
       <c r="C118" t="s">
         <v>1</v>
@@ -1860,7 +1860,7 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>0.009727076350741338</v>
+        <v>0.01094991665490165</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -1877,7 +1877,7 @@
         <v>49</v>
       </c>
       <c r="B120">
-        <v>-0.009142763374277295</v>
+        <v>-0.01041786181109403</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -1992,7 +1992,7 @@
         <v>26</v>
       </c>
       <c r="B132">
-        <v>1.052631578947369</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="C132" t="s">
         <v>1</v>
@@ -2158,7 +2158,7 @@
         <v>22</v>
       </c>
       <c r="B147">
-        <v>3.187993818510205E-05</v>
+        <v>3.187993818510206E-05</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="B148">
-        <v>-0.003542215353900228</v>
+        <v>-0.003542215353900229</v>
       </c>
       <c r="C148" t="s">
         <v>31</v>
@@ -2307,7 +2307,7 @@
         <v>22</v>
       </c>
       <c r="B161">
-        <v>0.0001364630715455225</v>
+        <v>0.0001364630715455226</v>
       </c>
       <c r="C161" t="s">
         <v>23</v>
@@ -2720,7 +2720,7 @@
         <v>55</v>
       </c>
       <c r="B201">
-        <v>0.03703703699289491</v>
+        <v>0.02992083939216329</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -2737,7 +2737,7 @@
         <v>56</v>
       </c>
       <c r="B202">
-        <v>4.306056313349053E-10</v>
+        <v>3.478702127009897E-10</v>
       </c>
       <c r="D202" t="s">
         <v>57</v>
@@ -2754,7 +2754,7 @@
         <v>59</v>
       </c>
       <c r="B203">
-        <v>1.076514078337263E-11</v>
+        <v>8.696755317524743E-12</v>
       </c>
       <c r="D203" t="s">
         <v>60</v>
@@ -2771,7 +2771,7 @@
         <v>61</v>
       </c>
       <c r="B204">
-        <v>1.076514078337263E-11</v>
+        <v>8.696755317524743E-12</v>
       </c>
       <c r="D204" t="s">
         <v>60</v>
@@ -2822,7 +2822,7 @@
         <v>3</v>
       </c>
       <c r="B207">
-        <v>5.475906008205881</v>
+        <v>4.61591735407015</v>
       </c>
       <c r="C207" t="s">
         <v>1</v>
@@ -2839,7 +2839,7 @@
         <v>62</v>
       </c>
       <c r="B208">
-        <v>0.0002387144822499921</v>
+        <v>0.0001928485176974507</v>
       </c>
       <c r="C208" t="s">
         <v>1</v>
@@ -2856,7 +2856,7 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>0.1828728005504997</v>
+        <v>0.1480567296772163</v>
       </c>
       <c r="C209" t="s">
         <v>23</v>
@@ -2873,7 +2873,7 @@
         <v>45</v>
       </c>
       <c r="B210">
-        <v>3.710106376980726E-09</v>
+        <v>0.5981054503816838</v>
       </c>
       <c r="C210" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>64</v>
       </c>
       <c r="B211">
-        <v>0.00985663081262526</v>
+        <v>0.007962804031785392</v>
       </c>
       <c r="C211" t="s">
         <v>31</v>
@@ -2907,7 +2907,7 @@
         <v>65</v>
       </c>
       <c r="B212">
-        <v>-3.992330849280697E-16</v>
+        <v>-3.225255037670057E-16</v>
       </c>
       <c r="C212" t="s">
         <v>31</v>
@@ -2924,7 +2924,7 @@
         <v>49</v>
       </c>
       <c r="B213">
-        <v>-0.005475906007014034</v>
+        <v>-0.004423780017658552</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
